--- a/data/nzd0089/nzd0089.xlsx
+++ b/data/nzd0089/nzd0089.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G315"/>
+  <dimension ref="A1:G316"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8943,6 +8943,33 @@
       <c r="G315" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B316" t="n">
+        <v>357.47</v>
+      </c>
+      <c r="C316" t="n">
+        <v>345.57</v>
+      </c>
+      <c r="D316" t="n">
+        <v>341.96</v>
+      </c>
+      <c r="E316" t="n">
+        <v>351.27</v>
+      </c>
+      <c r="F316" t="n">
+        <v>341.31</v>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -8957,7 +8984,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B329"/>
+  <dimension ref="A1:B330"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12250,6 +12277,16 @@
       </c>
       <c r="B329" t="n">
         <v>-0.46</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B330" t="n">
+        <v>0.59</v>
       </c>
     </row>
   </sheetData>
@@ -12418,28 +12455,28 @@
         <v>0.0485</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2080326397735634</v>
+        <v>-0.2091179762999976</v>
       </c>
       <c r="J2" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K2" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03597825531617183</v>
+        <v>0.03659138750194924</v>
       </c>
       <c r="M2" t="n">
-        <v>6.041782147435694</v>
+        <v>6.027646876573098</v>
       </c>
       <c r="N2" t="n">
-        <v>60.21010220474567</v>
+        <v>60.02737879755836</v>
       </c>
       <c r="O2" t="n">
-        <v>7.759516879596672</v>
+        <v>7.747733784633954</v>
       </c>
       <c r="P2" t="n">
-        <v>364.6765655940764</v>
+        <v>364.6886009340397</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -12496,28 +12533,28 @@
         <v>0.0477</v>
       </c>
       <c r="I3" t="n">
-        <v>0.002872121322009193</v>
+        <v>-0.002395959203035354</v>
       </c>
       <c r="J3" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K3" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L3" t="n">
-        <v>1.304569674731582e-05</v>
+        <v>9.089794469341328e-06</v>
       </c>
       <c r="M3" t="n">
-        <v>4.14147743844825</v>
+        <v>4.151274143990298</v>
       </c>
       <c r="N3" t="n">
-        <v>32.8316184006934</v>
+        <v>32.92576123876122</v>
       </c>
       <c r="O3" t="n">
-        <v>5.729888166508435</v>
+        <v>5.738097353545094</v>
       </c>
       <c r="P3" t="n">
-        <v>353.4431239717308</v>
+        <v>353.5015419264652</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -12574,28 +12611,28 @@
         <v>0.04</v>
       </c>
       <c r="I4" t="n">
-        <v>0.043544825044277</v>
+        <v>0.03881830971922448</v>
       </c>
       <c r="J4" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K4" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00414287732086438</v>
+        <v>0.003296837419082599</v>
       </c>
       <c r="M4" t="n">
-        <v>3.720906791505259</v>
+        <v>3.728281436854999</v>
       </c>
       <c r="N4" t="n">
-        <v>23.66615663283695</v>
+        <v>23.75070716603885</v>
       </c>
       <c r="O4" t="n">
-        <v>4.864787419079785</v>
+        <v>4.87346972556913</v>
       </c>
       <c r="P4" t="n">
-        <v>347.9201257056723</v>
+        <v>347.972538222337</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -12652,28 +12689,28 @@
         <v>0.0407</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1143594641850559</v>
+        <v>0.1106488479233216</v>
       </c>
       <c r="J5" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K5" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03905276721263773</v>
+        <v>0.03669959271342105</v>
       </c>
       <c r="M5" t="n">
-        <v>3.247239530134911</v>
+        <v>3.25305230552957</v>
       </c>
       <c r="N5" t="n">
-        <v>16.70904487369017</v>
+        <v>16.75441583240983</v>
       </c>
       <c r="O5" t="n">
-        <v>4.087669858695804</v>
+        <v>4.093215830176785</v>
       </c>
       <c r="P5" t="n">
-        <v>353.8073977458164</v>
+        <v>353.8485449173116</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -12730,28 +12767,28 @@
         <v>0.0404</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1117033143197425</v>
+        <v>0.1080621707552351</v>
       </c>
       <c r="J6" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K6" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03743142567359659</v>
+        <v>0.03516871182982806</v>
       </c>
       <c r="M6" t="n">
-        <v>3.328919098078509</v>
+        <v>3.336015640999421</v>
       </c>
       <c r="N6" t="n">
-        <v>16.66046437509166</v>
+        <v>16.70233884969168</v>
       </c>
       <c r="O6" t="n">
-        <v>4.081723211474739</v>
+        <v>4.08684950171788</v>
       </c>
       <c r="P6" t="n">
-        <v>343.8153063901153</v>
+        <v>343.8556831761043</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -12789,7 +12826,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G315"/>
+  <dimension ref="A1:G316"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24447,6 +24484,43 @@
         </is>
       </c>
     </row>
+    <row r="316">
+      <c r="A316" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>-35.55553513540737,174.4742478810482</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>-35.5560896408984,174.4748501194252</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>-35.556586429968995,174.4755132861446</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>-35.55699514533381,174.47629522571435</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>-35.55728855604357,174.4771399773992</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0089/nzd0089.xlsx
+++ b/data/nzd0089/nzd0089.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G316"/>
+  <dimension ref="A1:G318"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8968,6 +8968,60 @@
         <v>341.31</v>
       </c>
       <c r="G316" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:11:24+00:00</t>
+        </is>
+      </c>
+      <c r="B317" t="n">
+        <v>355.67</v>
+      </c>
+      <c r="C317" t="n">
+        <v>343.49</v>
+      </c>
+      <c r="D317" t="n">
+        <v>338.81</v>
+      </c>
+      <c r="E317" t="n">
+        <v>348.82</v>
+      </c>
+      <c r="F317" t="n">
+        <v>339.38</v>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B318" t="n">
+        <v>358.07</v>
+      </c>
+      <c r="C318" t="n">
+        <v>345.35</v>
+      </c>
+      <c r="D318" t="n">
+        <v>340.73</v>
+      </c>
+      <c r="E318" t="n">
+        <v>349.87</v>
+      </c>
+      <c r="F318" t="n">
+        <v>341.46</v>
+      </c>
+      <c r="G318" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -8984,7 +9038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B330"/>
+  <dimension ref="A1:B332"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12287,6 +12341,26 @@
       </c>
       <c r="B330" t="n">
         <v>0.59</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B331" t="n">
+        <v>-0.44</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B332" t="n">
+        <v>0.48</v>
       </c>
     </row>
   </sheetData>
@@ -12455,28 +12529,28 @@
         <v>0.0485</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2091179762999976</v>
+        <v>-0.2119999357951852</v>
       </c>
       <c r="J2" t="n">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="K2" t="n">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03659138750194924</v>
+        <v>0.03807043441899316</v>
       </c>
       <c r="M2" t="n">
-        <v>6.027646876573098</v>
+        <v>6.00283904505355</v>
       </c>
       <c r="N2" t="n">
-        <v>60.02737879755836</v>
+        <v>59.68782765874331</v>
       </c>
       <c r="O2" t="n">
-        <v>7.747733784633954</v>
+        <v>7.725789775728001</v>
       </c>
       <c r="P2" t="n">
-        <v>364.6886009340397</v>
+        <v>364.7206479565689</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -12533,28 +12607,28 @@
         <v>0.0477</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.002395959203035354</v>
+        <v>-0.01418806107585859</v>
       </c>
       <c r="J3" t="n">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="K3" t="n">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="L3" t="n">
-        <v>9.089794469341328e-06</v>
+        <v>0.0003183387793261883</v>
       </c>
       <c r="M3" t="n">
-        <v>4.151274143990298</v>
+        <v>4.177258247873833</v>
       </c>
       <c r="N3" t="n">
-        <v>32.92576123876122</v>
+        <v>33.22593037727827</v>
       </c>
       <c r="O3" t="n">
-        <v>5.738097353545094</v>
+        <v>5.764193818503873</v>
       </c>
       <c r="P3" t="n">
-        <v>353.5015419264652</v>
+        <v>353.6326939390806</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -12611,28 +12685,28 @@
         <v>0.04</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03881830971922448</v>
+        <v>0.02673411708706342</v>
       </c>
       <c r="J4" t="n">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="K4" t="n">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="L4" t="n">
-        <v>0.003296837419082599</v>
+        <v>0.001554101020976417</v>
       </c>
       <c r="M4" t="n">
-        <v>3.728281436854999</v>
+        <v>3.75416562894544</v>
       </c>
       <c r="N4" t="n">
-        <v>23.75070716603885</v>
+        <v>24.13436390124248</v>
       </c>
       <c r="O4" t="n">
-        <v>4.87346972556913</v>
+        <v>4.912673803667661</v>
       </c>
       <c r="P4" t="n">
-        <v>347.972538222337</v>
+        <v>348.1069388081066</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -12689,28 +12763,28 @@
         <v>0.0407</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1106488479233216</v>
+        <v>0.1008725845277489</v>
       </c>
       <c r="J5" t="n">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="K5" t="n">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03669959271342105</v>
+        <v>0.03050762932822049</v>
       </c>
       <c r="M5" t="n">
-        <v>3.25305230552957</v>
+        <v>3.276404977191388</v>
       </c>
       <c r="N5" t="n">
-        <v>16.75441583240983</v>
+        <v>16.9957801620611</v>
       </c>
       <c r="O5" t="n">
-        <v>4.093215830176785</v>
+        <v>4.122593863341513</v>
       </c>
       <c r="P5" t="n">
-        <v>353.8485449173116</v>
+        <v>353.9572782912401</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -12767,28 +12841,28 @@
         <v>0.0404</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1080621707552351</v>
+        <v>0.09978129808708917</v>
       </c>
       <c r="J6" t="n">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="K6" t="n">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03516871182982806</v>
+        <v>0.03011861205099264</v>
       </c>
       <c r="M6" t="n">
-        <v>3.336015640999421</v>
+        <v>3.355215140660692</v>
       </c>
       <c r="N6" t="n">
-        <v>16.70233884969168</v>
+        <v>16.85158841356213</v>
       </c>
       <c r="O6" t="n">
-        <v>4.08684950171788</v>
+        <v>4.105068624708012</v>
       </c>
       <c r="P6" t="n">
-        <v>343.8556831761043</v>
+        <v>343.9477807627199</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -12826,7 +12900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G316"/>
+  <dimension ref="A1:G318"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24521,6 +24595,80 @@
         </is>
       </c>
     </row>
+    <row r="317">
+      <c r="A317" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:11:24+00:00</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>-35.55554761895331,174.4742351959248</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>-35.556104078330804,174.47483547867228</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>-35.55660844574321,174.4754913392126</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>-35.55701478490929,174.4762828622617</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>-35.55730531920511,174.4771342775551</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>-35.55553097422512,174.4742521094218</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>-35.556091167934596,174.47484857088426</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>-35.55659502660509,174.4755047163916</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>-35.55700636794851,174.476288160885</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>-35.557287253207186,174.47714042039215</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0089/nzd0089.xlsx
+++ b/data/nzd0089/nzd0089.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G318"/>
+  <dimension ref="A1:G319"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9022,6 +9022,33 @@
         <v>341.46</v>
       </c>
       <c r="G318" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:45+00:00</t>
+        </is>
+      </c>
+      <c r="B319" t="n">
+        <v>358.34</v>
+      </c>
+      <c r="C319" t="n">
+        <v>345.45</v>
+      </c>
+      <c r="D319" t="n">
+        <v>340.03</v>
+      </c>
+      <c r="E319" t="n">
+        <v>349.57</v>
+      </c>
+      <c r="F319" t="n">
+        <v>340.82</v>
+      </c>
+      <c r="G319" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -9038,7 +9065,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B332"/>
+  <dimension ref="A1:B333"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12361,6 +12388,16 @@
       </c>
       <c r="B332" t="n">
         <v>0.48</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B333" t="n">
+        <v>-0.44</v>
       </c>
     </row>
   </sheetData>
@@ -12529,28 +12566,28 @@
         <v>0.0485</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2119999357951852</v>
+        <v>-0.2124362633630848</v>
       </c>
       <c r="J2" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="K2" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03807043441899316</v>
+        <v>0.03848619038724765</v>
       </c>
       <c r="M2" t="n">
-        <v>6.00283904505355</v>
+        <v>5.985937347695762</v>
       </c>
       <c r="N2" t="n">
-        <v>59.68782765874331</v>
+        <v>59.50151952968246</v>
       </c>
       <c r="O2" t="n">
-        <v>7.725789775728001</v>
+        <v>7.713722806121727</v>
       </c>
       <c r="P2" t="n">
-        <v>364.7206479565689</v>
+        <v>364.7255198899036</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -12607,28 +12644,28 @@
         <v>0.0477</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.01418806107585859</v>
+        <v>-0.01928000459534455</v>
       </c>
       <c r="J3" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="K3" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0003183387793261883</v>
+        <v>0.0005885662025848504</v>
       </c>
       <c r="M3" t="n">
-        <v>4.177258247873833</v>
+        <v>4.186646053909588</v>
       </c>
       <c r="N3" t="n">
-        <v>33.22593037727827</v>
+        <v>33.31067298299017</v>
       </c>
       <c r="O3" t="n">
-        <v>5.764193818503873</v>
+        <v>5.771539914354761</v>
       </c>
       <c r="P3" t="n">
-        <v>353.6326939390806</v>
+        <v>353.6895494100521</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -12685,28 +12722,28 @@
         <v>0.04</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02673411708706342</v>
+        <v>0.02099064523720316</v>
       </c>
       <c r="J4" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="K4" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001554101020976417</v>
+        <v>0.0009560135067728792</v>
       </c>
       <c r="M4" t="n">
-        <v>3.75416562894544</v>
+        <v>3.765565758286183</v>
       </c>
       <c r="N4" t="n">
-        <v>24.13436390124248</v>
+        <v>24.29921849669655</v>
       </c>
       <c r="O4" t="n">
-        <v>4.912673803667661</v>
+        <v>4.929423748948405</v>
       </c>
       <c r="P4" t="n">
-        <v>348.1069388081066</v>
+        <v>348.1710690946632</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -12763,28 +12800,28 @@
         <v>0.0407</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1008725845277489</v>
+        <v>0.09623229318025854</v>
       </c>
       <c r="J5" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="K5" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03050762932822049</v>
+        <v>0.0277869158236419</v>
       </c>
       <c r="M5" t="n">
-        <v>3.276404977191388</v>
+        <v>3.28743422191957</v>
       </c>
       <c r="N5" t="n">
-        <v>16.9957801620611</v>
+        <v>17.09948116059197</v>
       </c>
       <c r="O5" t="n">
-        <v>4.122593863341513</v>
+        <v>4.135151890873172</v>
       </c>
       <c r="P5" t="n">
-        <v>353.9572782912401</v>
+        <v>354.0090907178698</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -12841,28 +12878,28 @@
         <v>0.0404</v>
       </c>
       <c r="I6" t="n">
-        <v>0.09978129808708917</v>
+        <v>0.09598406855973639</v>
       </c>
       <c r="J6" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="K6" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03011861205099264</v>
+        <v>0.02795877062094787</v>
       </c>
       <c r="M6" t="n">
-        <v>3.355215140660692</v>
+        <v>3.363094516248327</v>
       </c>
       <c r="N6" t="n">
-        <v>16.85158841356213</v>
+        <v>16.90382825168638</v>
       </c>
       <c r="O6" t="n">
-        <v>4.105068624708012</v>
+        <v>4.111426547037705</v>
       </c>
       <c r="P6" t="n">
-        <v>343.9477807627199</v>
+        <v>343.9901797548411</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -12900,7 +12937,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G318"/>
+  <dimension ref="A1:G319"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24669,6 +24706,43 @@
         </is>
       </c>
     </row>
+    <row r="319">
+      <c r="A319" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:45+00:00</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>-35.55552910169305,174.4742540121898</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>-35.55609047382724,174.4748492747665</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>-35.556599918999346,174.47549983929562</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>-35.55700877279449,174.47628664699275</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>-35.5572928119758,174.4771385302887</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
